--- a/data/nzd0220/nzd0220.xlsx
+++ b/data/nzd0220/nzd0220.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R416"/>
+  <dimension ref="A1:R418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25418,6 +25418,126 @@
         <v>378.89</v>
       </c>
       <c r="R416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>377.79</v>
+      </c>
+      <c r="C417" t="n">
+        <v>378.01</v>
+      </c>
+      <c r="D417" t="n">
+        <v>380.74</v>
+      </c>
+      <c r="E417" t="n">
+        <v>383.58</v>
+      </c>
+      <c r="F417" t="n">
+        <v>380.85</v>
+      </c>
+      <c r="G417" t="n">
+        <v>383.62</v>
+      </c>
+      <c r="H417" t="n">
+        <v>389.11</v>
+      </c>
+      <c r="I417" t="n">
+        <v>386.23</v>
+      </c>
+      <c r="J417" t="n">
+        <v>378.68</v>
+      </c>
+      <c r="K417" t="n">
+        <v>374.49</v>
+      </c>
+      <c r="L417" t="n">
+        <v>374.73</v>
+      </c>
+      <c r="M417" t="n">
+        <v>377.34</v>
+      </c>
+      <c r="N417" t="n">
+        <v>379.24</v>
+      </c>
+      <c r="O417" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="P417" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>377.18</v>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>377.72</v>
+      </c>
+      <c r="C418" t="n">
+        <v>377.61</v>
+      </c>
+      <c r="D418" t="n">
+        <v>379.9</v>
+      </c>
+      <c r="E418" t="n">
+        <v>381.96</v>
+      </c>
+      <c r="F418" t="n">
+        <v>379.05</v>
+      </c>
+      <c r="G418" t="n">
+        <v>382.33</v>
+      </c>
+      <c r="H418" t="n">
+        <v>388.21</v>
+      </c>
+      <c r="I418" t="n">
+        <v>385.35</v>
+      </c>
+      <c r="J418" t="n">
+        <v>376.62</v>
+      </c>
+      <c r="K418" t="n">
+        <v>373.2</v>
+      </c>
+      <c r="L418" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="M418" t="n">
+        <v>374.92</v>
+      </c>
+      <c r="N418" t="n">
+        <v>376.76</v>
+      </c>
+      <c r="O418" t="n">
+        <v>375.76</v>
+      </c>
+      <c r="P418" t="n">
+        <v>371.47</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>376.3</v>
+      </c>
+      <c r="R418" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25434,7 +25554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B420"/>
+  <dimension ref="A1:B422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29637,6 +29757,26 @@
       </c>
       <c r="B420" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -29805,28 +29945,28 @@
         <v>0.0468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5643187748156993</v>
+        <v>0.5601592495567832</v>
       </c>
       <c r="J2" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K2" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4572618536952299</v>
+        <v>0.4548689626559222</v>
       </c>
       <c r="M2" t="n">
-        <v>3.627447561773018</v>
+        <v>3.630071203681334</v>
       </c>
       <c r="N2" t="n">
-        <v>21.07065740973853</v>
+        <v>21.06780471497251</v>
       </c>
       <c r="O2" t="n">
-        <v>4.590278576485149</v>
+        <v>4.589967833762293</v>
       </c>
       <c r="P2" t="n">
-        <v>367.517399205286</v>
+        <v>367.5602517726887</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -29887,28 +30027,28 @@
         <v>0.0542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.914080833054471</v>
+        <v>0.907624717709302</v>
       </c>
       <c r="J3" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K3" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6472570929330868</v>
+        <v>0.6441269387897143</v>
       </c>
       <c r="M3" t="n">
-        <v>3.989546742542626</v>
+        <v>4.005332753405442</v>
       </c>
       <c r="N3" t="n">
-        <v>25.3836685974758</v>
+        <v>25.49869396322043</v>
       </c>
       <c r="O3" t="n">
-        <v>5.038220776968373</v>
+        <v>5.049623150614353</v>
       </c>
       <c r="P3" t="n">
-        <v>360.9197643202014</v>
+        <v>360.9862784292465</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29965,28 +30105,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1.032207932970449</v>
+        <v>1.026807056156787</v>
       </c>
       <c r="J4" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K4" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7151824778638213</v>
+        <v>0.7136081427959287</v>
       </c>
       <c r="M4" t="n">
-        <v>3.694251515209513</v>
+        <v>3.705993192182242</v>
       </c>
       <c r="N4" t="n">
-        <v>23.65309280872177</v>
+        <v>23.70610553138254</v>
       </c>
       <c r="O4" t="n">
-        <v>4.863444541548898</v>
+        <v>4.868891612203186</v>
       </c>
       <c r="P4" t="n">
-        <v>359.174924153179</v>
+        <v>359.2305692636018</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30043,28 +30183,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9867720827360457</v>
+        <v>0.9812411590149877</v>
       </c>
       <c r="J5" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K5" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7215580691703793</v>
+        <v>0.7195714027440769</v>
       </c>
       <c r="M5" t="n">
-        <v>3.634863381668092</v>
+        <v>3.648382574682568</v>
       </c>
       <c r="N5" t="n">
-        <v>20.94598411594484</v>
+        <v>21.0223650655166</v>
       </c>
       <c r="O5" t="n">
-        <v>4.57667828407731</v>
+        <v>4.585015274294798</v>
       </c>
       <c r="P5" t="n">
-        <v>362.9608612740038</v>
+        <v>363.017849953116</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30121,28 +30261,28 @@
         <v>0.0858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8236720918753176</v>
+        <v>0.8183840535044988</v>
       </c>
       <c r="J6" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K6" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5815559520700562</v>
+        <v>0.5793528101159653</v>
       </c>
       <c r="M6" t="n">
-        <v>4.220229545591642</v>
+        <v>4.230519069968998</v>
       </c>
       <c r="N6" t="n">
-        <v>27.21186481786895</v>
+        <v>27.24399843588648</v>
       </c>
       <c r="O6" t="n">
-        <v>5.216499287632363</v>
+        <v>5.219578377214627</v>
       </c>
       <c r="P6" t="n">
-        <v>364.1486238772056</v>
+        <v>364.2031111630939</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30199,28 +30339,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7241314090983216</v>
+        <v>0.7204821395330411</v>
       </c>
       <c r="J7" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K7" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5185186946298236</v>
+        <v>0.5177317569479583</v>
       </c>
       <c r="M7" t="n">
-        <v>4.286763113941974</v>
+        <v>4.288659657775552</v>
       </c>
       <c r="N7" t="n">
-        <v>27.14272793835519</v>
+        <v>27.09018397499517</v>
       </c>
       <c r="O7" t="n">
-        <v>5.209868322554342</v>
+        <v>5.204823145409954</v>
       </c>
       <c r="P7" t="n">
-        <v>367.9890684798849</v>
+        <v>368.0266703844267</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30277,28 +30417,28 @@
         <v>0.058</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4974649439043665</v>
+        <v>0.4941617180289866</v>
       </c>
       <c r="J8" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K8" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4126440938101457</v>
+        <v>0.4110171814506421</v>
       </c>
       <c r="M8" t="n">
-        <v>3.599907826525154</v>
+        <v>3.600432659899849</v>
       </c>
       <c r="N8" t="n">
-        <v>19.63606145848529</v>
+        <v>19.6048038476545</v>
       </c>
       <c r="O8" t="n">
-        <v>4.431259579226349</v>
+        <v>4.42773123028651</v>
       </c>
       <c r="P8" t="n">
-        <v>379.235441262176</v>
+        <v>379.2694761919981</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30355,28 +30495,28 @@
         <v>0.0577</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6197046027711827</v>
+        <v>0.6160173646225225</v>
       </c>
       <c r="J9" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K9" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4835748166792968</v>
+        <v>0.4821911850464398</v>
       </c>
       <c r="M9" t="n">
-        <v>3.957658607632314</v>
+        <v>3.955814151343135</v>
       </c>
       <c r="N9" t="n">
-        <v>22.86214067922057</v>
+        <v>22.83062166622157</v>
       </c>
       <c r="O9" t="n">
-        <v>4.781437093512846</v>
+        <v>4.778139979764256</v>
       </c>
       <c r="P9" t="n">
-        <v>373.5819236145924</v>
+        <v>373.6199146546829</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30433,28 +30573,28 @@
         <v>0.0703</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8308099636709564</v>
+        <v>0.8253815828276171</v>
       </c>
       <c r="J10" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K10" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5484574248663219</v>
+        <v>0.5462916666399523</v>
       </c>
       <c r="M10" t="n">
-        <v>4.694471602499084</v>
+        <v>4.698303032088589</v>
       </c>
       <c r="N10" t="n">
-        <v>31.67837462218164</v>
+        <v>31.698841053122</v>
       </c>
       <c r="O10" t="n">
-        <v>5.628354521721391</v>
+        <v>5.630172382185291</v>
       </c>
       <c r="P10" t="n">
-        <v>361.8100068522033</v>
+        <v>361.8659412619147</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30511,28 +30651,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7778744420867518</v>
+        <v>0.7748066465258446</v>
       </c>
       <c r="J11" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K11" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4791248649983897</v>
+        <v>0.4792246852954476</v>
       </c>
       <c r="M11" t="n">
-        <v>5.103668367465761</v>
+        <v>5.094276848315047</v>
       </c>
       <c r="N11" t="n">
-        <v>36.66972337486881</v>
+        <v>36.54934008935899</v>
       </c>
       <c r="O11" t="n">
-        <v>6.055553102307733</v>
+        <v>6.045605022606008</v>
       </c>
       <c r="P11" t="n">
-        <v>356.8128538823365</v>
+        <v>356.844465367208</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30589,28 +30729,28 @@
         <v>0.0635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7601211772740493</v>
+        <v>0.7580838792558769</v>
       </c>
       <c r="J12" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K12" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3888418856337882</v>
+        <v>0.3897752684523809</v>
       </c>
       <c r="M12" t="n">
-        <v>6.055002261372535</v>
+        <v>6.035573997481523</v>
       </c>
       <c r="N12" t="n">
-        <v>50.62323784541864</v>
+        <v>50.40709903709778</v>
       </c>
       <c r="O12" t="n">
-        <v>7.115000902699776</v>
+        <v>7.099795703898653</v>
       </c>
       <c r="P12" t="n">
-        <v>356.2362621093803</v>
+        <v>356.2572586587381</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30667,28 +30807,28 @@
         <v>0.0636</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7672235481251122</v>
+        <v>0.7653021459877434</v>
       </c>
       <c r="J13" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K13" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4109695574982895</v>
+        <v>0.4119883305367696</v>
       </c>
       <c r="M13" t="n">
-        <v>5.897085928329783</v>
+        <v>5.877621315480224</v>
       </c>
       <c r="N13" t="n">
-        <v>47.03007254399563</v>
+        <v>46.83263007992088</v>
       </c>
       <c r="O13" t="n">
-        <v>6.857847515364834</v>
+        <v>6.843437007814193</v>
       </c>
       <c r="P13" t="n">
-        <v>358.114193803382</v>
+        <v>358.1340004950878</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30745,28 +30885,28 @@
         <v>0.0607</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7900661283088884</v>
+        <v>0.7859159650243475</v>
       </c>
       <c r="J14" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K14" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L14" t="n">
-        <v>0.364661084221589</v>
+        <v>0.3640927610565265</v>
       </c>
       <c r="M14" t="n">
-        <v>6.744101577836534</v>
+        <v>6.73409104965259</v>
       </c>
       <c r="N14" t="n">
-        <v>60.62428611470539</v>
+        <v>60.43876792206896</v>
       </c>
       <c r="O14" t="n">
-        <v>7.786159908112945</v>
+        <v>7.774237449555356</v>
       </c>
       <c r="P14" t="n">
-        <v>361.8310806927695</v>
+        <v>361.8738487648732</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30823,28 +30963,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5866238933994378</v>
+        <v>0.5825369571205294</v>
       </c>
       <c r="J15" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K15" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2716647209481179</v>
+        <v>0.2704345064406757</v>
       </c>
       <c r="M15" t="n">
-        <v>6.163809349777704</v>
+        <v>6.157964301654901</v>
       </c>
       <c r="N15" t="n">
-        <v>51.43056695228163</v>
+        <v>51.28977587433627</v>
       </c>
       <c r="O15" t="n">
-        <v>7.171510785900111</v>
+        <v>7.161688060390251</v>
       </c>
       <c r="P15" t="n">
-        <v>366.3755192787629</v>
+        <v>366.4176386370489</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30901,28 +31041,28 @@
         <v>0.0795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2995136860464915</v>
+        <v>0.2977192807771762</v>
       </c>
       <c r="J16" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K16" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09790669422240239</v>
+        <v>0.09767372032038035</v>
       </c>
       <c r="M16" t="n">
-        <v>5.744251410891725</v>
+        <v>5.727218767030285</v>
       </c>
       <c r="N16" t="n">
-        <v>46.07614427591233</v>
+        <v>45.87556796990906</v>
       </c>
       <c r="O16" t="n">
-        <v>6.787941092548781</v>
+        <v>6.77315052024603</v>
       </c>
       <c r="P16" t="n">
-        <v>366.2514261043231</v>
+        <v>366.269918981531</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30979,28 +31119,28 @@
         <v>0.0578</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1079096058119186</v>
+        <v>-0.1052273591501132</v>
       </c>
       <c r="J17" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K17" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L17" t="n">
-        <v>0.008583167723053009</v>
+        <v>0.008240575723079124</v>
       </c>
       <c r="M17" t="n">
-        <v>7.156893028570023</v>
+        <v>7.136127732844797</v>
       </c>
       <c r="N17" t="n">
-        <v>74.97778628907444</v>
+        <v>74.65996461150499</v>
       </c>
       <c r="O17" t="n">
-        <v>8.658971433667768</v>
+        <v>8.640599783088266</v>
       </c>
       <c r="P17" t="n">
-        <v>376.6284626873142</v>
+        <v>376.600834067279</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31038,7 +31178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R416"/>
+  <dimension ref="A1:R418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69313,6 +69453,190 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-37.74429062867909,176.47045745868922</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-37.74494116133705,176.47081808826965</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-37.74557787810311,176.47120169426165</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-37.74618490129512,176.47161440959766</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-37.746781025228415,176.47207166146066</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-37.74735830587373,176.47259049767914</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-37.7479154373575,176.47314522730392</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-37.748516822276855,176.4736231615929</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-37.749137326624215,176.47406325522326</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-37.74973020913714,176.4745564890409</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-37.750302063615145,176.47509296478265</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-37.750871278631834,176.47563389843043</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-37.75144377205656,176.4761654798086</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-37.752024002769026,176.47667083310085</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>-37.752613770593015,176.47717803607733</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>-37.75318534074681,176.47771728885303</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-37.74429089373403,176.47045673867055</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-37.74494267594599,176.47081397384773</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-37.745581222060885,176.4711931522343</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-37.746192441034665,176.47159868711003</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-37.74679024815815,176.47205488093417</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-37.74736499534912,176.4725785416537</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-37.747920152773176,176.47313692906354</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-37.74852146278299,176.47361507475594</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-37.74914846967192,176.47404458447352</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-37.74973731740973,176.47454492228565</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-37.75031069005646,176.47507857807742</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-37.75088418317942,176.4756117903846</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-37.75145697835305,176.4761428066363</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-37.75204088242498,176.47664370014056</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-37.752621041490855,176.47716605426004</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-37.7531898706201,176.4777091026505</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0220/nzd0220.xlsx
+++ b/data/nzd0220/nzd0220.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R418"/>
+  <dimension ref="A1:R419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25538,6 +25538,66 @@
         <v>376.3</v>
       </c>
       <c r="R418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>378.02</v>
+      </c>
+      <c r="C419" t="n">
+        <v>377.43</v>
+      </c>
+      <c r="D419" t="n">
+        <v>379.75</v>
+      </c>
+      <c r="E419" t="n">
+        <v>382.01</v>
+      </c>
+      <c r="F419" t="n">
+        <v>379.51</v>
+      </c>
+      <c r="G419" t="n">
+        <v>382.49</v>
+      </c>
+      <c r="H419" t="n">
+        <v>388.39</v>
+      </c>
+      <c r="I419" t="n">
+        <v>385.79</v>
+      </c>
+      <c r="J419" t="n">
+        <v>377.16</v>
+      </c>
+      <c r="K419" t="n">
+        <v>373.47</v>
+      </c>
+      <c r="L419" t="n">
+        <v>372.98</v>
+      </c>
+      <c r="M419" t="n">
+        <v>374.35</v>
+      </c>
+      <c r="N419" t="n">
+        <v>375.75</v>
+      </c>
+      <c r="O419" t="n">
+        <v>375.38</v>
+      </c>
+      <c r="P419" t="n">
+        <v>371.11</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>375.96</v>
+      </c>
+      <c r="R419" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25554,7 +25614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B422"/>
+  <dimension ref="A1:B423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29777,6 +29837,16 @@
       </c>
       <c r="B422" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -29945,28 +30015,28 @@
         <v>0.0468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5601592495567832</v>
+        <v>0.5582183905010638</v>
       </c>
       <c r="J2" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K2" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4548689626559222</v>
+        <v>0.4538552880224395</v>
       </c>
       <c r="M2" t="n">
-        <v>3.630071203681334</v>
+        <v>3.630781669729899</v>
       </c>
       <c r="N2" t="n">
-        <v>21.06780471497251</v>
+        <v>21.06047422830406</v>
       </c>
       <c r="O2" t="n">
-        <v>4.589967833762293</v>
+        <v>4.589169230732732</v>
       </c>
       <c r="P2" t="n">
-        <v>367.5602517726887</v>
+        <v>367.5803093163506</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30027,28 +30097,28 @@
         <v>0.0542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.907624717709302</v>
+        <v>0.9042447368368303</v>
       </c>
       <c r="J3" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K3" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6441269387897143</v>
+        <v>0.6423636858803726</v>
       </c>
       <c r="M3" t="n">
-        <v>4.005332753405442</v>
+        <v>4.014079567757518</v>
       </c>
       <c r="N3" t="n">
-        <v>25.49869396322043</v>
+        <v>25.56831692318139</v>
       </c>
       <c r="O3" t="n">
-        <v>5.049623150614353</v>
+        <v>5.05651232799658</v>
       </c>
       <c r="P3" t="n">
-        <v>360.9862784292465</v>
+        <v>361.0212083813861</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30105,28 +30175,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1.026807056156787</v>
+        <v>1.02385859683619</v>
       </c>
       <c r="J4" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K4" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7136081427959287</v>
+        <v>0.7125759060956767</v>
       </c>
       <c r="M4" t="n">
-        <v>3.705993192182242</v>
+        <v>3.713124614515663</v>
       </c>
       <c r="N4" t="n">
-        <v>23.70610553138254</v>
+        <v>23.74879246360424</v>
       </c>
       <c r="O4" t="n">
-        <v>4.868891612203186</v>
+        <v>4.873273280209538</v>
       </c>
       <c r="P4" t="n">
-        <v>359.2305692636018</v>
+        <v>359.2610397150155</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30183,28 +30253,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9812411590149877</v>
+        <v>0.9781420439470946</v>
       </c>
       <c r="J5" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K5" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7195714027440769</v>
+        <v>0.7182276958706428</v>
       </c>
       <c r="M5" t="n">
-        <v>3.648382574682568</v>
+        <v>3.656919941581597</v>
       </c>
       <c r="N5" t="n">
-        <v>21.0223650655166</v>
+        <v>21.08188992874173</v>
       </c>
       <c r="O5" t="n">
-        <v>4.585015274294798</v>
+        <v>4.591501925159318</v>
       </c>
       <c r="P5" t="n">
-        <v>363.017849953116</v>
+        <v>363.0498773358382</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30261,28 +30331,28 @@
         <v>0.0858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8183840535044988</v>
+        <v>0.815558675689693</v>
       </c>
       <c r="J6" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K6" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5793528101159653</v>
+        <v>0.57804375282975</v>
       </c>
       <c r="M6" t="n">
-        <v>4.230519069968998</v>
+        <v>4.236595620492079</v>
       </c>
       <c r="N6" t="n">
-        <v>27.24399843588648</v>
+        <v>27.27009593855632</v>
       </c>
       <c r="O6" t="n">
-        <v>5.219578377214627</v>
+        <v>5.22207774152744</v>
       </c>
       <c r="P6" t="n">
-        <v>364.2031111630939</v>
+        <v>364.2323096454436</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30339,28 +30409,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7204821395330411</v>
+        <v>0.7184438038610391</v>
       </c>
       <c r="J7" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K7" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5177317569479583</v>
+        <v>0.5171019177298695</v>
       </c>
       <c r="M7" t="n">
-        <v>4.288659657775552</v>
+        <v>4.290947462411091</v>
       </c>
       <c r="N7" t="n">
-        <v>27.09018397499517</v>
+        <v>27.07288086782623</v>
       </c>
       <c r="O7" t="n">
-        <v>5.204823145409954</v>
+        <v>5.203160661350583</v>
       </c>
       <c r="P7" t="n">
-        <v>368.0266703844267</v>
+        <v>368.047735286908</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30417,28 +30487,28 @@
         <v>0.058</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4941617180289866</v>
+        <v>0.4923973406789362</v>
       </c>
       <c r="J8" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K8" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4110171814506421</v>
+        <v>0.4100318263471379</v>
       </c>
       <c r="M8" t="n">
-        <v>3.600432659899849</v>
+        <v>3.601241306960325</v>
       </c>
       <c r="N8" t="n">
-        <v>19.6048038476545</v>
+        <v>19.59349662492119</v>
       </c>
       <c r="O8" t="n">
-        <v>4.42773123028651</v>
+        <v>4.426454181952095</v>
       </c>
       <c r="P8" t="n">
-        <v>379.2694761919981</v>
+        <v>379.2877099095008</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30495,28 +30565,28 @@
         <v>0.0577</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6160173646225225</v>
+        <v>0.6141827446789382</v>
       </c>
       <c r="J9" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K9" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4821911850464398</v>
+        <v>0.4815037379133865</v>
       </c>
       <c r="M9" t="n">
-        <v>3.955814151343135</v>
+        <v>3.954870288529559</v>
       </c>
       <c r="N9" t="n">
-        <v>22.83062166622157</v>
+        <v>22.81448771351912</v>
       </c>
       <c r="O9" t="n">
-        <v>4.778139979764256</v>
+        <v>4.776451372464616</v>
       </c>
       <c r="P9" t="n">
-        <v>373.6199146546829</v>
+        <v>373.638874284705</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30573,28 +30643,28 @@
         <v>0.0703</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8253815828276171</v>
+        <v>0.8224661218910168</v>
       </c>
       <c r="J10" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K10" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5462916666399523</v>
+        <v>0.5449912219148726</v>
       </c>
       <c r="M10" t="n">
-        <v>4.698303032088589</v>
+        <v>4.701320319570626</v>
       </c>
       <c r="N10" t="n">
-        <v>31.698841053122</v>
+        <v>31.72019413904453</v>
       </c>
       <c r="O10" t="n">
-        <v>5.630172382185291</v>
+        <v>5.632068371304145</v>
       </c>
       <c r="P10" t="n">
-        <v>361.8659412619147</v>
+        <v>361.8960706960217</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30651,28 +30721,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7748066465258446</v>
+        <v>0.7731034182506631</v>
       </c>
       <c r="J11" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K11" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4792246852954476</v>
+        <v>0.479122233218627</v>
       </c>
       <c r="M11" t="n">
-        <v>5.094276848315047</v>
+        <v>5.090393819129682</v>
       </c>
       <c r="N11" t="n">
-        <v>36.54934008935899</v>
+        <v>36.4950712323205</v>
       </c>
       <c r="O11" t="n">
-        <v>6.045605022606008</v>
+        <v>6.041115065310418</v>
       </c>
       <c r="P11" t="n">
-        <v>356.844465367208</v>
+        <v>356.8620671479221</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30729,28 +30799,28 @@
         <v>0.0635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7580838792558769</v>
+        <v>0.7566231989653421</v>
       </c>
       <c r="J12" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K12" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3897752684523809</v>
+        <v>0.3899079501133034</v>
       </c>
       <c r="M12" t="n">
-        <v>6.035573997481523</v>
+        <v>6.028016284833111</v>
       </c>
       <c r="N12" t="n">
-        <v>50.40709903709778</v>
+        <v>50.31090323211867</v>
       </c>
       <c r="O12" t="n">
-        <v>7.099795703898653</v>
+        <v>7.093017921316615</v>
       </c>
       <c r="P12" t="n">
-        <v>356.2572586587381</v>
+        <v>356.2723538603279</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30807,28 +30877,28 @@
         <v>0.0636</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7653021459877434</v>
+        <v>0.7635261226545689</v>
       </c>
       <c r="J13" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K13" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4119883305367696</v>
+        <v>0.4118627845784405</v>
       </c>
       <c r="M13" t="n">
-        <v>5.877621315480224</v>
+        <v>5.871646908220916</v>
       </c>
       <c r="N13" t="n">
-        <v>46.83263007992088</v>
+        <v>46.75665595550742</v>
       </c>
       <c r="O13" t="n">
-        <v>6.843437007814193</v>
+        <v>6.837883879937376</v>
       </c>
       <c r="P13" t="n">
-        <v>358.1340004950878</v>
+        <v>358.1523545664175</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30885,28 +30955,28 @@
         <v>0.0607</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7859159650243475</v>
+        <v>0.7828278649069784</v>
       </c>
       <c r="J14" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K14" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3640927610565265</v>
+        <v>0.362986599187879</v>
       </c>
       <c r="M14" t="n">
-        <v>6.73409104965259</v>
+        <v>6.734471604609794</v>
       </c>
       <c r="N14" t="n">
-        <v>60.43876792206896</v>
+        <v>60.40321592526202</v>
       </c>
       <c r="O14" t="n">
-        <v>7.774237449555356</v>
+        <v>7.771950586903008</v>
       </c>
       <c r="P14" t="n">
-        <v>361.8738487648732</v>
+        <v>361.905762315089</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30963,28 +31033,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5825369571205294</v>
+        <v>0.5796422888314026</v>
       </c>
       <c r="J15" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K15" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2704345064406757</v>
+        <v>0.2690687185062743</v>
       </c>
       <c r="M15" t="n">
-        <v>6.157964301654901</v>
+        <v>6.159910118330523</v>
       </c>
       <c r="N15" t="n">
-        <v>51.28977587433627</v>
+        <v>51.26287938201362</v>
       </c>
       <c r="O15" t="n">
-        <v>7.161688060390251</v>
+        <v>7.159810010189769</v>
       </c>
       <c r="P15" t="n">
-        <v>366.4176386370489</v>
+        <v>366.4475531923716</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31041,28 +31111,28 @@
         <v>0.0795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2977192807771762</v>
+        <v>0.2963605229015857</v>
       </c>
       <c r="J16" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K16" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09767372032038035</v>
+        <v>0.09725942535474408</v>
       </c>
       <c r="M16" t="n">
-        <v>5.727218767030285</v>
+        <v>5.72142111953288</v>
       </c>
       <c r="N16" t="n">
-        <v>45.87556796990906</v>
+        <v>45.78692744132861</v>
       </c>
       <c r="O16" t="n">
-        <v>6.77315052024603</v>
+        <v>6.766603833632394</v>
       </c>
       <c r="P16" t="n">
-        <v>366.269918981531</v>
+        <v>366.2839608798004</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31119,28 +31189,28 @@
         <v>0.0578</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1052273591501132</v>
+        <v>-0.1042568604104343</v>
       </c>
       <c r="J17" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K17" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L17" t="n">
-        <v>0.008240575723079124</v>
+        <v>0.008128750177908373</v>
       </c>
       <c r="M17" t="n">
-        <v>7.136127732844797</v>
+        <v>7.123920998870779</v>
       </c>
       <c r="N17" t="n">
-        <v>74.65996461150499</v>
+        <v>74.49212153196223</v>
       </c>
       <c r="O17" t="n">
-        <v>8.640599783088266</v>
+        <v>8.630881851349967</v>
       </c>
       <c r="P17" t="n">
-        <v>376.600834067279</v>
+        <v>376.590804580188</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31178,7 +31248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R418"/>
+  <dimension ref="A1:R419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69637,6 +69707,98 @@
         </is>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-37.74428975778418,176.47045982446483</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-37.744943357519986,176.47081212235778</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-37.74558181919613,176.47119162687218</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-37.74619220832669,176.47159917237204</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-37.74678789118743,176.47205916929136</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-37.747364165646815,176.47258002457167</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-37.74791920969009,176.4731385887117</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-37.748519142529986,176.47361911817455</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-37.7491455486791,176.47404947874824</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-37.74973582963183,176.4745473432346</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-37.75031155812594,176.47507713035847</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-37.750887222679744,176.47560658311644</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-37.75146235672264,176.47613357280167</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-37.75204299238157,176.47664030851965</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>-37.75262300955324,176.47716281106096</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>-37.753191620798276,176.4777059397992</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0220/nzd0220.xlsx
+++ b/data/nzd0220/nzd0220.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R419"/>
+  <dimension ref="A1:R420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25600,6 +25600,66 @@
       <c r="R419" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 21:59:44+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="C420" t="n">
+        <v>375.6</v>
+      </c>
+      <c r="D420" t="n">
+        <v>376.67</v>
+      </c>
+      <c r="E420" t="n">
+        <v>380.32</v>
+      </c>
+      <c r="F420" t="n">
+        <v>377.38</v>
+      </c>
+      <c r="G420" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="H420" t="n">
+        <v>385.89</v>
+      </c>
+      <c r="I420" t="n">
+        <v>383.96</v>
+      </c>
+      <c r="J420" t="n">
+        <v>374.39</v>
+      </c>
+      <c r="K420" t="n">
+        <v>370.25</v>
+      </c>
+      <c r="L420" t="n">
+        <v>369.83</v>
+      </c>
+      <c r="M420" t="n">
+        <v>370.2</v>
+      </c>
+      <c r="N420" t="n">
+        <v>372.38</v>
+      </c>
+      <c r="O420" t="n">
+        <v>374.73</v>
+      </c>
+      <c r="P420" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25614,7 +25674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B423"/>
+  <dimension ref="A1:B424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29847,6 +29907,16 @@
       </c>
       <c r="B423" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -30015,28 +30085,28 @@
         <v>0.0468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5582183905010638</v>
+        <v>0.55633685213446</v>
       </c>
       <c r="J2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4538552880224395</v>
+        <v>0.452949778985329</v>
       </c>
       <c r="M2" t="n">
-        <v>3.630781669729899</v>
+        <v>3.631125889658304</v>
       </c>
       <c r="N2" t="n">
-        <v>21.06047422830406</v>
+        <v>21.05003975854756</v>
       </c>
       <c r="O2" t="n">
-        <v>4.589169230732732</v>
+        <v>4.588032231637825</v>
       </c>
       <c r="P2" t="n">
-        <v>367.5803093163506</v>
+        <v>367.5998933431011</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30097,28 +30167,28 @@
         <v>0.0542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9042447368368303</v>
+        <v>0.8999667080848012</v>
       </c>
       <c r="J3" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K3" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6423636858803726</v>
+        <v>0.6394796348475091</v>
       </c>
       <c r="M3" t="n">
-        <v>4.014079567757518</v>
+        <v>4.027796010415125</v>
       </c>
       <c r="N3" t="n">
-        <v>25.56831692318139</v>
+        <v>25.71319771636916</v>
       </c>
       <c r="O3" t="n">
-        <v>5.05651232799658</v>
+        <v>5.070818249195011</v>
       </c>
       <c r="P3" t="n">
-        <v>361.0212083813861</v>
+        <v>361.0657363224615</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30175,28 +30245,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1.02385859683619</v>
+        <v>1.019428780703307</v>
       </c>
       <c r="J4" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K4" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7125759060956767</v>
+        <v>0.7099153895105974</v>
       </c>
       <c r="M4" t="n">
-        <v>3.713124614515663</v>
+        <v>3.728401982887536</v>
       </c>
       <c r="N4" t="n">
-        <v>23.74879246360424</v>
+        <v>23.91288616434597</v>
       </c>
       <c r="O4" t="n">
-        <v>4.873273280209538</v>
+        <v>4.890080384241753</v>
       </c>
       <c r="P4" t="n">
-        <v>359.2610397150155</v>
+        <v>359.3071475378407</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30253,28 +30323,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9781420439470946</v>
+        <v>0.9741996796601243</v>
       </c>
       <c r="J5" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K5" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7182276958706428</v>
+        <v>0.7159221497794671</v>
       </c>
       <c r="M5" t="n">
-        <v>3.656919941581597</v>
+        <v>3.670026757638154</v>
       </c>
       <c r="N5" t="n">
-        <v>21.08188992874173</v>
+        <v>21.20643449848908</v>
       </c>
       <c r="O5" t="n">
-        <v>4.591501925159318</v>
+        <v>4.605044462162019</v>
       </c>
       <c r="P5" t="n">
-        <v>363.0498773358382</v>
+        <v>363.0909115071454</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30331,28 +30401,28 @@
         <v>0.0858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.815558675689693</v>
+        <v>0.811698673316877</v>
       </c>
       <c r="J6" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K6" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L6" t="n">
-        <v>0.57804375282975</v>
+        <v>0.5754468090433034</v>
       </c>
       <c r="M6" t="n">
-        <v>4.236595620492079</v>
+        <v>4.24835403623678</v>
       </c>
       <c r="N6" t="n">
-        <v>27.27009593855632</v>
+        <v>27.37264168956059</v>
       </c>
       <c r="O6" t="n">
-        <v>5.22207774152744</v>
+        <v>5.231887010396974</v>
       </c>
       <c r="P6" t="n">
-        <v>364.2323096454436</v>
+        <v>364.2724865512501</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30409,28 +30479,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7184438038610391</v>
+        <v>0.7152076395460764</v>
       </c>
       <c r="J7" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K7" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5171019177298695</v>
+        <v>0.5150067159866012</v>
       </c>
       <c r="M7" t="n">
-        <v>4.290947462411091</v>
+        <v>4.30037644647439</v>
       </c>
       <c r="N7" t="n">
-        <v>27.07288086782623</v>
+        <v>27.12609252078283</v>
       </c>
       <c r="O7" t="n">
-        <v>5.203160661350583</v>
+        <v>5.208271548295349</v>
       </c>
       <c r="P7" t="n">
-        <v>368.047735286908</v>
+        <v>368.0814189627969</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30487,28 +30557,28 @@
         <v>0.058</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4923973406789362</v>
+        <v>0.489454148142914</v>
       </c>
       <c r="J8" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K8" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4100318263471379</v>
+        <v>0.4071390955984885</v>
       </c>
       <c r="M8" t="n">
-        <v>3.601241306960325</v>
+        <v>3.60826224422886</v>
       </c>
       <c r="N8" t="n">
-        <v>19.59349662492119</v>
+        <v>19.64419102378851</v>
       </c>
       <c r="O8" t="n">
-        <v>4.426454181952095</v>
+        <v>4.432176781649003</v>
       </c>
       <c r="P8" t="n">
-        <v>379.2877099095008</v>
+        <v>379.3183441832316</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30565,28 +30635,28 @@
         <v>0.0577</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6141827446789382</v>
+        <v>0.61146749463578</v>
       </c>
       <c r="J9" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K9" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4815037379133865</v>
+        <v>0.479629969638471</v>
       </c>
       <c r="M9" t="n">
-        <v>3.954870288529559</v>
+        <v>3.957887345991447</v>
       </c>
       <c r="N9" t="n">
-        <v>22.81448771351912</v>
+        <v>22.84298377605345</v>
       </c>
       <c r="O9" t="n">
-        <v>4.776451372464616</v>
+        <v>4.779433415798723</v>
       </c>
       <c r="P9" t="n">
-        <v>373.638874284705</v>
+        <v>373.6671360147996</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30643,28 +30713,28 @@
         <v>0.0703</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8224661218910168</v>
+        <v>0.8182206019709739</v>
       </c>
       <c r="J10" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K10" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5449912219148726</v>
+        <v>0.5420770761973162</v>
       </c>
       <c r="M10" t="n">
-        <v>4.701320319570626</v>
+        <v>4.710579167278983</v>
       </c>
       <c r="N10" t="n">
-        <v>31.72019413904453</v>
+        <v>31.84727521455715</v>
       </c>
       <c r="O10" t="n">
-        <v>5.632068371304145</v>
+        <v>5.643339012903367</v>
       </c>
       <c r="P10" t="n">
-        <v>361.8960706960217</v>
+        <v>361.9402602683205</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30721,28 +30791,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7731034182506631</v>
+        <v>0.7698664045476326</v>
       </c>
       <c r="J11" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K11" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L11" t="n">
-        <v>0.479122233218627</v>
+        <v>0.4774674574809724</v>
       </c>
       <c r="M11" t="n">
-        <v>5.090393819129682</v>
+        <v>5.093747821982795</v>
       </c>
       <c r="N11" t="n">
-        <v>36.4950712323205</v>
+        <v>36.52585741588974</v>
       </c>
       <c r="O11" t="n">
-        <v>6.041115065310418</v>
+        <v>6.043662582895386</v>
       </c>
       <c r="P11" t="n">
-        <v>356.8620671479221</v>
+        <v>356.8957596646824</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30799,28 +30869,28 @@
         <v>0.0635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7566231989653421</v>
+        <v>0.7536662856722943</v>
       </c>
       <c r="J12" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K12" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3899079501133034</v>
+        <v>0.3887675420966473</v>
       </c>
       <c r="M12" t="n">
-        <v>6.028016284833111</v>
+        <v>6.027311171626042</v>
       </c>
       <c r="N12" t="n">
-        <v>50.31090323211867</v>
+        <v>50.28919717746264</v>
       </c>
       <c r="O12" t="n">
-        <v>7.093017921316615</v>
+        <v>7.091487656159505</v>
       </c>
       <c r="P12" t="n">
-        <v>356.2723538603279</v>
+        <v>356.3031309468109</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30877,28 +30947,28 @@
         <v>0.0636</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7635261226545689</v>
+        <v>0.7597914061737578</v>
       </c>
       <c r="J13" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K13" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4118627845784405</v>
+        <v>0.409884546865838</v>
       </c>
       <c r="M13" t="n">
-        <v>5.871646908220916</v>
+        <v>5.874327385914065</v>
       </c>
       <c r="N13" t="n">
-        <v>46.75665595550742</v>
+        <v>46.80198934082876</v>
       </c>
       <c r="O13" t="n">
-        <v>6.837883879937376</v>
+        <v>6.841197946327</v>
       </c>
       <c r="P13" t="n">
-        <v>358.1523545664175</v>
+        <v>358.191227431709</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30955,28 +31025,28 @@
         <v>0.0607</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7828278649069784</v>
+        <v>0.7781369815395636</v>
       </c>
       <c r="J14" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K14" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L14" t="n">
-        <v>0.362986599187879</v>
+        <v>0.3604175283589539</v>
       </c>
       <c r="M14" t="n">
-        <v>6.734471604609794</v>
+        <v>6.743046929150609</v>
       </c>
       <c r="N14" t="n">
-        <v>60.40321592526202</v>
+        <v>60.50661786176126</v>
       </c>
       <c r="O14" t="n">
-        <v>7.771950586903008</v>
+        <v>7.77859999368532</v>
       </c>
       <c r="P14" t="n">
-        <v>361.905762315089</v>
+        <v>361.9545874610342</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31033,28 +31103,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5796422888314026</v>
+        <v>0.576411692758416</v>
       </c>
       <c r="J15" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K15" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2690687185062743</v>
+        <v>0.2674044801057175</v>
       </c>
       <c r="M15" t="n">
-        <v>6.159910118330523</v>
+        <v>6.16354421981781</v>
       </c>
       <c r="N15" t="n">
-        <v>51.26287938201362</v>
+        <v>51.25795322486213</v>
       </c>
       <c r="O15" t="n">
-        <v>7.159810010189769</v>
+        <v>7.159465987408707</v>
       </c>
       <c r="P15" t="n">
-        <v>366.4475531923716</v>
+        <v>366.4811789111113</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31111,28 +31181,28 @@
         <v>0.0795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2963605229015857</v>
+        <v>0.2939806385972742</v>
       </c>
       <c r="J16" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K16" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09725942535474408</v>
+        <v>0.09616510064491868</v>
       </c>
       <c r="M16" t="n">
-        <v>5.72142111953288</v>
+        <v>5.721388964073973</v>
       </c>
       <c r="N16" t="n">
-        <v>45.78692744132861</v>
+        <v>45.74137241700654</v>
       </c>
       <c r="O16" t="n">
-        <v>6.766603833632394</v>
+        <v>6.763236829877137</v>
       </c>
       <c r="P16" t="n">
-        <v>366.2839608798004</v>
+        <v>366.308731949424</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31189,28 +31259,28 @@
         <v>0.0578</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1042568604104343</v>
+        <v>-0.1038821126798678</v>
       </c>
       <c r="J17" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K17" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L17" t="n">
-        <v>0.008128750177908373</v>
+        <v>0.008110786987872265</v>
       </c>
       <c r="M17" t="n">
-        <v>7.123920998870779</v>
+        <v>7.108768212145796</v>
       </c>
       <c r="N17" t="n">
-        <v>74.49212153196223</v>
+        <v>74.31591602549018</v>
       </c>
       <c r="O17" t="n">
-        <v>8.630881851349967</v>
+        <v>8.62066795703733</v>
       </c>
       <c r="P17" t="n">
-        <v>376.590804580188</v>
+        <v>376.5869040115307</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31248,7 +31318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R419"/>
+  <dimension ref="A1:R420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69799,6 +69869,98 @@
         </is>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 21:59:44+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-37.74428892475424,176.47046208738055</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-37.744950286853886,176.4707932988749</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-37.74559408036923,176.47116030609783</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-37.746200073855405,176.47158277051426</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-37.746798804985445,176.4720393123308</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-37.74737712974353,176.472556853974</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-37.747932308064456,176.47311553803888</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-37.74852879267231,176.47360230122732</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-37.74916053228845,176.47402437292732</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-37.749753572757925,176.47451847117014</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-37.750328648240455,176.4750486283845</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-37.75090935236873,176.4755686705371</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>-37.75148030236689,176.47610276286835</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>-37.75204660151764,176.47663450706233</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>-37.75263492726258,176.47714317168504</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>-37.75319836413111,176.4776937535179</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0220/nzd0220.xlsx
+++ b/data/nzd0220/nzd0220.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R420"/>
+  <dimension ref="A1:R422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25660,6 +25660,126 @@
       <c r="R420" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:59:45+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>378.95</v>
+      </c>
+      <c r="C421" t="n">
+        <v>374.9</v>
+      </c>
+      <c r="D421" t="n">
+        <v>376.7</v>
+      </c>
+      <c r="E421" t="n">
+        <v>380.37</v>
+      </c>
+      <c r="F421" t="n">
+        <v>377.99</v>
+      </c>
+      <c r="G421" t="n">
+        <v>379.78</v>
+      </c>
+      <c r="H421" t="n">
+        <v>386.26</v>
+      </c>
+      <c r="I421" t="n">
+        <v>382.27</v>
+      </c>
+      <c r="J421" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="K421" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="L421" t="n">
+        <v>368.01</v>
+      </c>
+      <c r="M421" t="n">
+        <v>369.27</v>
+      </c>
+      <c r="N421" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="O421" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="P421" t="n">
+        <v>368.49</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>379.08</v>
+      </c>
+      <c r="C422" t="n">
+        <v>375</v>
+      </c>
+      <c r="D422" t="n">
+        <v>377.31</v>
+      </c>
+      <c r="E422" t="n">
+        <v>380.93</v>
+      </c>
+      <c r="F422" t="n">
+        <v>378.48</v>
+      </c>
+      <c r="G422" t="n">
+        <v>380.51</v>
+      </c>
+      <c r="H422" t="n">
+        <v>386.69</v>
+      </c>
+      <c r="I422" t="n">
+        <v>381.96</v>
+      </c>
+      <c r="J422" t="n">
+        <v>373.32</v>
+      </c>
+      <c r="K422" t="n">
+        <v>368.99</v>
+      </c>
+      <c r="L422" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="M422" t="n">
+        <v>370.07</v>
+      </c>
+      <c r="N422" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="O422" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="P422" t="n">
+        <v>369.09</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>375.95</v>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25674,7 +25794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B424"/>
+  <dimension ref="A1:B426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29917,6 +30037,26 @@
       </c>
       <c r="B424" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>
@@ -30085,28 +30225,28 @@
         <v>0.0468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.55633685213446</v>
+        <v>0.5532905426953372</v>
       </c>
       <c r="J2" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K2" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L2" t="n">
-        <v>0.452949778985329</v>
+        <v>0.4520891862454232</v>
       </c>
       <c r="M2" t="n">
-        <v>3.631125889658304</v>
+        <v>3.628383462230371</v>
       </c>
       <c r="N2" t="n">
-        <v>21.05003975854756</v>
+        <v>21.00232272821932</v>
       </c>
       <c r="O2" t="n">
-        <v>4.588032231637825</v>
+        <v>4.582829118374295</v>
       </c>
       <c r="P2" t="n">
-        <v>367.5998933431011</v>
+        <v>367.6317276185082</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30167,28 +30307,28 @@
         <v>0.0542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8999667080848012</v>
+        <v>0.8908620670015787</v>
       </c>
       <c r="J3" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K3" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6394796348475091</v>
+        <v>0.6329027065623299</v>
       </c>
       <c r="M3" t="n">
-        <v>4.027796010415125</v>
+        <v>4.057907243886351</v>
       </c>
       <c r="N3" t="n">
-        <v>25.71319771636916</v>
+        <v>26.057949890333</v>
       </c>
       <c r="O3" t="n">
-        <v>5.070818249195011</v>
+        <v>5.1046988050553</v>
       </c>
       <c r="P3" t="n">
-        <v>361.0657363224615</v>
+        <v>361.1608819644252</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30245,28 +30385,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1.019428780703307</v>
+        <v>1.010911539794391</v>
       </c>
       <c r="J4" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K4" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7099153895105974</v>
+        <v>0.7049856160003973</v>
       </c>
       <c r="M4" t="n">
-        <v>3.728401982887536</v>
+        <v>3.757128616481891</v>
       </c>
       <c r="N4" t="n">
-        <v>23.91288616434597</v>
+        <v>24.20830177534706</v>
       </c>
       <c r="O4" t="n">
-        <v>4.890080384241753</v>
+        <v>4.920193266056432</v>
       </c>
       <c r="P4" t="n">
-        <v>359.3071475378407</v>
+        <v>359.3961522852808</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30323,28 +30463,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9741996796601243</v>
+        <v>0.9666515232053053</v>
       </c>
       <c r="J5" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K5" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7159221497794671</v>
+        <v>0.7117010180565525</v>
       </c>
       <c r="M5" t="n">
-        <v>3.670026757638154</v>
+        <v>3.694325398823903</v>
       </c>
       <c r="N5" t="n">
-        <v>21.20643449848908</v>
+        <v>21.42695620242791</v>
       </c>
       <c r="O5" t="n">
-        <v>4.605044462162019</v>
+        <v>4.62892603121155</v>
       </c>
       <c r="P5" t="n">
-        <v>363.0909115071454</v>
+        <v>363.1697892622516</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30401,28 +30541,28 @@
         <v>0.0858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.811698673316877</v>
+        <v>0.8047973732179627</v>
       </c>
       <c r="J6" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K6" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5754468090433034</v>
+        <v>0.5713162596408888</v>
       </c>
       <c r="M6" t="n">
-        <v>4.24835403623678</v>
+        <v>4.267091444435311</v>
       </c>
       <c r="N6" t="n">
-        <v>27.37264168956059</v>
+        <v>27.51114136491728</v>
       </c>
       <c r="O6" t="n">
-        <v>5.231887010396974</v>
+        <v>5.245106420742793</v>
       </c>
       <c r="P6" t="n">
-        <v>364.2724865512501</v>
+        <v>364.344604801569</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30479,28 +30619,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7152076395460764</v>
+        <v>0.7089116141723208</v>
       </c>
       <c r="J7" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K7" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5150067159866012</v>
+        <v>0.5110235964498988</v>
       </c>
       <c r="M7" t="n">
-        <v>4.30037644647439</v>
+        <v>4.317854849774951</v>
       </c>
       <c r="N7" t="n">
-        <v>27.12609252078283</v>
+        <v>27.2211338977051</v>
       </c>
       <c r="O7" t="n">
-        <v>5.208271548295349</v>
+        <v>5.217387650702705</v>
       </c>
       <c r="P7" t="n">
-        <v>368.0814189627969</v>
+        <v>368.1472107187095</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30557,28 +30697,28 @@
         <v>0.058</v>
       </c>
       <c r="I8" t="n">
-        <v>0.489454148142914</v>
+        <v>0.4841424667502688</v>
       </c>
       <c r="J8" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K8" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4071390955984885</v>
+        <v>0.402337632215084</v>
       </c>
       <c r="M8" t="n">
-        <v>3.60826224422886</v>
+        <v>3.619465942987143</v>
       </c>
       <c r="N8" t="n">
-        <v>19.64419102378851</v>
+        <v>19.71000314148358</v>
       </c>
       <c r="O8" t="n">
-        <v>4.432176781649003</v>
+        <v>4.439594929887589</v>
       </c>
       <c r="P8" t="n">
-        <v>379.3183441832316</v>
+        <v>379.3738507059998</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30635,28 +30775,28 @@
         <v>0.0577</v>
       </c>
       <c r="I9" t="n">
-        <v>0.61146749463578</v>
+        <v>0.6043830338785183</v>
       </c>
       <c r="J9" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K9" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L9" t="n">
-        <v>0.479629969638471</v>
+        <v>0.4732269235976014</v>
       </c>
       <c r="M9" t="n">
-        <v>3.957887345991447</v>
+        <v>3.971944935384687</v>
       </c>
       <c r="N9" t="n">
-        <v>22.84298377605345</v>
+        <v>23.01726587796726</v>
       </c>
       <c r="O9" t="n">
-        <v>4.779433415798723</v>
+        <v>4.797631277825262</v>
       </c>
       <c r="P9" t="n">
-        <v>373.6671360147996</v>
+        <v>373.7411721340072</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30713,28 +30853,28 @@
         <v>0.0703</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8182206019709739</v>
+        <v>0.8086208003662239</v>
       </c>
       <c r="J10" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K10" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5420770761973162</v>
+        <v>0.5346576851524656</v>
       </c>
       <c r="M10" t="n">
-        <v>4.710579167278983</v>
+        <v>4.734614707978499</v>
       </c>
       <c r="N10" t="n">
-        <v>31.84727521455715</v>
+        <v>32.21525922644736</v>
       </c>
       <c r="O10" t="n">
-        <v>5.643339012903367</v>
+        <v>5.675848767052146</v>
       </c>
       <c r="P10" t="n">
-        <v>361.9402602683205</v>
+        <v>362.0405788928134</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30791,28 +30931,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7698664045476326</v>
+        <v>0.7622158284978292</v>
       </c>
       <c r="J11" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K11" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4774674574809724</v>
+        <v>0.4727285865577232</v>
       </c>
       <c r="M11" t="n">
-        <v>5.093747821982795</v>
+        <v>5.106180611338945</v>
       </c>
       <c r="N11" t="n">
-        <v>36.52585741588974</v>
+        <v>36.6820305513145</v>
       </c>
       <c r="O11" t="n">
-        <v>6.043662582895386</v>
+        <v>6.056569206350614</v>
       </c>
       <c r="P11" t="n">
-        <v>356.8957596646824</v>
+        <v>356.9757097302931</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30869,28 +31009,28 @@
         <v>0.0635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7536662856722943</v>
+        <v>0.7461717933563277</v>
       </c>
       <c r="J12" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K12" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3887675420966473</v>
+        <v>0.3849039817780817</v>
       </c>
       <c r="M12" t="n">
-        <v>6.027311171626042</v>
+        <v>6.032884232124621</v>
       </c>
       <c r="N12" t="n">
-        <v>50.28919717746264</v>
+        <v>50.36667118233732</v>
       </c>
       <c r="O12" t="n">
-        <v>7.091487656159505</v>
+        <v>7.096948018855522</v>
       </c>
       <c r="P12" t="n">
-        <v>356.3031309468109</v>
+        <v>356.3814499032266</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30947,28 +31087,28 @@
         <v>0.0636</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7597914061737578</v>
+        <v>0.7518832998895356</v>
       </c>
       <c r="J13" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K13" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L13" t="n">
-        <v>0.409884546865838</v>
+        <v>0.4054232892598837</v>
       </c>
       <c r="M13" t="n">
-        <v>5.874327385914065</v>
+        <v>5.881449261960145</v>
       </c>
       <c r="N13" t="n">
-        <v>46.80198934082876</v>
+        <v>46.93265896612409</v>
       </c>
       <c r="O13" t="n">
-        <v>6.841197946327</v>
+        <v>6.850741490242067</v>
       </c>
       <c r="P13" t="n">
-        <v>358.191227431709</v>
+        <v>358.2738655569951</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31025,28 +31165,28 @@
         <v>0.0607</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7781369815395636</v>
+        <v>0.769317124780533</v>
       </c>
       <c r="J14" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K14" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3604175283589539</v>
+        <v>0.3558083410806088</v>
       </c>
       <c r="M14" t="n">
-        <v>6.743046929150609</v>
+        <v>6.756778408713934</v>
       </c>
       <c r="N14" t="n">
-        <v>60.50661786176126</v>
+        <v>60.65754832937955</v>
       </c>
       <c r="O14" t="n">
-        <v>7.77859999368532</v>
+        <v>7.788295598484918</v>
       </c>
       <c r="P14" t="n">
-        <v>361.9545874610342</v>
+        <v>362.0467553826462</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31103,28 +31243,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>0.576411692758416</v>
+        <v>0.5693678310285142</v>
       </c>
       <c r="J15" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K15" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2674044801057175</v>
+        <v>0.2634923963876332</v>
       </c>
       <c r="M15" t="n">
-        <v>6.16354421981781</v>
+        <v>6.173763749468506</v>
       </c>
       <c r="N15" t="n">
-        <v>51.25795322486213</v>
+        <v>51.29441494220067</v>
       </c>
       <c r="O15" t="n">
-        <v>7.159465987408707</v>
+        <v>7.162011933961062</v>
       </c>
       <c r="P15" t="n">
-        <v>366.4811789111113</v>
+        <v>366.5547924252729</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31181,28 +31321,28 @@
         <v>0.0795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2939806385972742</v>
+        <v>0.2891351622391499</v>
       </c>
       <c r="J16" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K16" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09616510064491868</v>
+        <v>0.09391614869009546</v>
       </c>
       <c r="M16" t="n">
-        <v>5.721388964073973</v>
+        <v>5.721602060354674</v>
       </c>
       <c r="N16" t="n">
-        <v>45.74137241700654</v>
+        <v>45.65675243239261</v>
       </c>
       <c r="O16" t="n">
-        <v>6.763236829877137</v>
+        <v>6.756978054751444</v>
       </c>
       <c r="P16" t="n">
-        <v>366.308731949424</v>
+        <v>366.3593656573291</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31259,28 +31399,28 @@
         <v>0.0578</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1038821126798678</v>
+        <v>-0.1026659569532702</v>
       </c>
       <c r="J17" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K17" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L17" t="n">
-        <v>0.008110786987872265</v>
+        <v>0.008001278160498781</v>
       </c>
       <c r="M17" t="n">
-        <v>7.108768212145796</v>
+        <v>7.080918877271926</v>
       </c>
       <c r="N17" t="n">
-        <v>74.31591602549018</v>
+        <v>73.97410918378398</v>
       </c>
       <c r="O17" t="n">
-        <v>8.62066795703733</v>
+        <v>8.600820262264756</v>
       </c>
       <c r="P17" t="n">
-        <v>376.5869040115307</v>
+        <v>376.5741873424562</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31318,7 +31458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R420"/>
+  <dimension ref="A1:R422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69961,6 +70101,190 @@
         </is>
       </c>
     </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:59:45+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-37.744286236339114,176.47046939042644</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-37.744952937418006,176.47078609863453</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-37.74559396094226,176.47116061117035</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-37.746199841147494,176.47158325577638</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-37.74679567943798,176.47204499906658</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-37.747378218727455,176.4725549076434</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-37.74793036950532,176.47311894953899</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-37.74853770455042,176.47358677081849</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-37.74916859206186,176.47401086834785</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-37.7497612320557,176.4745060077591</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-37.75033852252598,176.47503216057123</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-37.75091431155052,176.47556017446192</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>-37.751478598329776,176.47610568844132</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>-37.75204854489851,176.47663138320047</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>-37.75263733267144,176.4771392077735</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>-37.7531997539782,176.47769124184134</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-37.74428574409405,176.47047072760378</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-37.74495255876601,176.47078712724036</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-37.745591532593664,176.47116681431154</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-37.74619723481865,176.47158869071185</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-37.74679316875212,176.4720495670999</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-37.747374433211746,176.47256167345898</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-37.747928116585115,176.4731229142551</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-37.74853933927342,176.47358392204487</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-37.74916632017956,176.47401467500814</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-37.749760515718535,176.47450717340195</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-37.75033781721995,176.47503333684372</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-37.75091004558773,176.47556748291373</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>-37.75147625527863,176.4761097111039</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>-37.7520522650845,176.4766254032359</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>-37.75263405256842,176.47714461310733</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>-37.75319167227409,176.47770584677417</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0220/nzd0220.xlsx
+++ b/data/nzd0220/nzd0220.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R422"/>
+  <dimension ref="A1:R426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25778,6 +25778,246 @@
         <v>375.95</v>
       </c>
       <c r="R422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>380.28</v>
+      </c>
+      <c r="C423" t="n">
+        <v>375.68</v>
+      </c>
+      <c r="D423" t="n">
+        <v>377.96</v>
+      </c>
+      <c r="E423" t="n">
+        <v>381.71</v>
+      </c>
+      <c r="F423" t="n">
+        <v>379.14</v>
+      </c>
+      <c r="G423" t="n">
+        <v>381.28</v>
+      </c>
+      <c r="H423" t="n">
+        <v>387.15</v>
+      </c>
+      <c r="I423" t="n">
+        <v>382.21</v>
+      </c>
+      <c r="J423" t="n">
+        <v>374.05</v>
+      </c>
+      <c r="K423" t="n">
+        <v>369.08</v>
+      </c>
+      <c r="L423" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="M423" t="n">
+        <v>371.27</v>
+      </c>
+      <c r="N423" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="O423" t="n">
+        <v>373.29</v>
+      </c>
+      <c r="P423" t="n">
+        <v>369.49</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>377.03</v>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:59:31+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>380.79</v>
+      </c>
+      <c r="C424" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="D424" t="n">
+        <v>377.33</v>
+      </c>
+      <c r="E424" t="n">
+        <v>381.51</v>
+      </c>
+      <c r="F424" t="n">
+        <v>378.96</v>
+      </c>
+      <c r="G424" t="n">
+        <v>380.92</v>
+      </c>
+      <c r="H424" t="n">
+        <v>387.62</v>
+      </c>
+      <c r="I424" t="n">
+        <v>382.36</v>
+      </c>
+      <c r="J424" t="n">
+        <v>374.06</v>
+      </c>
+      <c r="K424" t="n">
+        <v>368.5</v>
+      </c>
+      <c r="L424" t="n">
+        <v>368.32</v>
+      </c>
+      <c r="M424" t="n">
+        <v>371.12</v>
+      </c>
+      <c r="N424" t="n">
+        <v>373.59</v>
+      </c>
+      <c r="O424" t="n">
+        <v>371.57</v>
+      </c>
+      <c r="P424" t="n">
+        <v>367.86</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>375.96</v>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:59:03+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>381.43</v>
+      </c>
+      <c r="C425" t="n">
+        <v>375.98</v>
+      </c>
+      <c r="D425" t="n">
+        <v>377.46</v>
+      </c>
+      <c r="E425" t="n">
+        <v>381.77</v>
+      </c>
+      <c r="F425" t="n">
+        <v>378.93</v>
+      </c>
+      <c r="G425" t="n">
+        <v>381.18</v>
+      </c>
+      <c r="H425" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="I425" t="n">
+        <v>382.51</v>
+      </c>
+      <c r="J425" t="n">
+        <v>374.04</v>
+      </c>
+      <c r="K425" t="n">
+        <v>367.52</v>
+      </c>
+      <c r="L425" t="n">
+        <v>367.49</v>
+      </c>
+      <c r="M425" t="n">
+        <v>370.72</v>
+      </c>
+      <c r="N425" t="n">
+        <v>373.27</v>
+      </c>
+      <c r="O425" t="n">
+        <v>370.8</v>
+      </c>
+      <c r="P425" t="n">
+        <v>366.7</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>376.35</v>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>381.78</v>
+      </c>
+      <c r="C426" t="n">
+        <v>376.44</v>
+      </c>
+      <c r="D426" t="n">
+        <v>377.77</v>
+      </c>
+      <c r="E426" t="n">
+        <v>382.4</v>
+      </c>
+      <c r="F426" t="n">
+        <v>379.72</v>
+      </c>
+      <c r="G426" t="n">
+        <v>381.91</v>
+      </c>
+      <c r="H426" t="n">
+        <v>388.92</v>
+      </c>
+      <c r="I426" t="n">
+        <v>383.06</v>
+      </c>
+      <c r="J426" t="n">
+        <v>374.16</v>
+      </c>
+      <c r="K426" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="L426" t="n">
+        <v>367.77</v>
+      </c>
+      <c r="M426" t="n">
+        <v>371.04</v>
+      </c>
+      <c r="N426" t="n">
+        <v>373.46</v>
+      </c>
+      <c r="O426" t="n">
+        <v>371.62</v>
+      </c>
+      <c r="P426" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>376.64</v>
+      </c>
+      <c r="R426" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25794,7 +26034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B426"/>
+  <dimension ref="A1:B430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30057,6 +30297,46 @@
       </c>
       <c r="B426" t="n">
         <v>-0.36</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>0.51</v>
       </c>
     </row>
   </sheetData>
@@ -30225,28 +30505,28 @@
         <v>0.0468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5532905426953372</v>
+        <v>0.5510105464276933</v>
       </c>
       <c r="J2" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K2" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4520891862454232</v>
+        <v>0.4547114033270746</v>
       </c>
       <c r="M2" t="n">
-        <v>3.628383462230371</v>
+        <v>3.604921753676527</v>
       </c>
       <c r="N2" t="n">
-        <v>21.00232272821932</v>
+        <v>20.8226143841386</v>
       </c>
       <c r="O2" t="n">
-        <v>4.582829118374295</v>
+        <v>4.56318029274963</v>
       </c>
       <c r="P2" t="n">
-        <v>367.6317276185082</v>
+        <v>367.6556255298736</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30307,28 +30587,28 @@
         <v>0.0542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8908620670015787</v>
+        <v>0.8750069595426314</v>
       </c>
       <c r="J3" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K3" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6329027065623299</v>
+        <v>0.6226566925859829</v>
       </c>
       <c r="M3" t="n">
-        <v>4.057907243886351</v>
+        <v>4.107139752556834</v>
       </c>
       <c r="N3" t="n">
-        <v>26.057949890333</v>
+        <v>26.53602511468338</v>
       </c>
       <c r="O3" t="n">
-        <v>5.1046988050553</v>
+        <v>5.151312950567396</v>
       </c>
       <c r="P3" t="n">
-        <v>361.1608819644252</v>
+        <v>361.3271456069626</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30385,28 +30665,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1.010911539794391</v>
+        <v>0.9954694573757481</v>
       </c>
       <c r="J4" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K4" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7049856160003973</v>
+        <v>0.6967492229177437</v>
       </c>
       <c r="M4" t="n">
-        <v>3.757128616481891</v>
+        <v>3.808070115008611</v>
       </c>
       <c r="N4" t="n">
-        <v>24.20830177534706</v>
+        <v>24.66642286671889</v>
       </c>
       <c r="O4" t="n">
-        <v>4.920193266056432</v>
+        <v>4.966530264351451</v>
       </c>
       <c r="P4" t="n">
-        <v>359.3961522852808</v>
+        <v>359.5580916480117</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30463,28 +30743,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9666515232053053</v>
+        <v>0.9541082753007765</v>
       </c>
       <c r="J5" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K5" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7117010180565525</v>
+        <v>0.7060159441805923</v>
       </c>
       <c r="M5" t="n">
-        <v>3.694325398823903</v>
+        <v>3.728645256315018</v>
       </c>
       <c r="N5" t="n">
-        <v>21.42695620242791</v>
+        <v>21.67851140109986</v>
       </c>
       <c r="O5" t="n">
-        <v>4.62892603121155</v>
+        <v>4.656018835990665</v>
       </c>
       <c r="P5" t="n">
-        <v>363.1697892622516</v>
+        <v>363.3013224744413</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30541,28 +30821,28 @@
         <v>0.0858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8047973732179627</v>
+        <v>0.7930923670523912</v>
       </c>
       <c r="J6" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K6" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5713162596408888</v>
+        <v>0.5654335436048329</v>
       </c>
       <c r="M6" t="n">
-        <v>4.267091444435311</v>
+        <v>4.292767614307616</v>
       </c>
       <c r="N6" t="n">
-        <v>27.51114136491728</v>
+        <v>27.64693781874201</v>
       </c>
       <c r="O6" t="n">
-        <v>5.245106420742793</v>
+        <v>5.258035547496993</v>
       </c>
       <c r="P6" t="n">
-        <v>364.344604801569</v>
+        <v>364.4673489735792</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30619,28 +30899,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7089116141723208</v>
+        <v>0.6987733071331342</v>
       </c>
       <c r="J7" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K7" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5110235964498988</v>
+        <v>0.506013036753465</v>
       </c>
       <c r="M7" t="n">
-        <v>4.317854849774951</v>
+        <v>4.338048362848476</v>
       </c>
       <c r="N7" t="n">
-        <v>27.2211338977051</v>
+        <v>27.26159482746188</v>
       </c>
       <c r="O7" t="n">
-        <v>5.217387650702705</v>
+        <v>5.221263719394174</v>
       </c>
       <c r="P7" t="n">
-        <v>368.1472107187095</v>
+        <v>368.2535241675046</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30697,28 +30977,28 @@
         <v>0.058</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4841424667502688</v>
+        <v>0.4767191065032322</v>
       </c>
       <c r="J8" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K8" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L8" t="n">
-        <v>0.402337632215084</v>
+        <v>0.397650330428575</v>
       </c>
       <c r="M8" t="n">
-        <v>3.619465942987143</v>
+        <v>3.625544123856279</v>
       </c>
       <c r="N8" t="n">
-        <v>19.71000314148358</v>
+        <v>19.68780545994116</v>
       </c>
       <c r="O8" t="n">
-        <v>4.439594929887589</v>
+        <v>4.437094258627054</v>
       </c>
       <c r="P8" t="n">
-        <v>379.3738507059998</v>
+        <v>379.4516830386358</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30775,28 +31055,28 @@
         <v>0.0577</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6043830338785183</v>
+        <v>0.5913946498605185</v>
       </c>
       <c r="J9" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K9" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4732269235976014</v>
+        <v>0.4620661733383032</v>
       </c>
       <c r="M9" t="n">
-        <v>3.971944935384687</v>
+        <v>3.994796786112533</v>
       </c>
       <c r="N9" t="n">
-        <v>23.01726587796726</v>
+        <v>23.28650571731058</v>
       </c>
       <c r="O9" t="n">
-        <v>4.797631277825262</v>
+        <v>4.82560936227857</v>
       </c>
       <c r="P9" t="n">
-        <v>373.7411721340072</v>
+        <v>373.8773723283205</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30853,28 +31133,28 @@
         <v>0.0703</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8086208003662239</v>
+        <v>0.791730940705796</v>
       </c>
       <c r="J10" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K10" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5346576851524656</v>
+        <v>0.5227266687100798</v>
       </c>
       <c r="M10" t="n">
-        <v>4.734614707978499</v>
+        <v>4.771345169536504</v>
       </c>
       <c r="N10" t="n">
-        <v>32.21525922644736</v>
+        <v>32.73200499078949</v>
       </c>
       <c r="O10" t="n">
-        <v>5.675848767052146</v>
+        <v>5.721189123843879</v>
       </c>
       <c r="P10" t="n">
-        <v>362.0405788928134</v>
+        <v>362.2176988399434</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30931,28 +31211,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7622158284978292</v>
+        <v>0.7460807408589123</v>
       </c>
       <c r="J11" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K11" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4727285865577232</v>
+        <v>0.4618826872810469</v>
       </c>
       <c r="M11" t="n">
-        <v>5.106180611338945</v>
+        <v>5.135086567865224</v>
       </c>
       <c r="N11" t="n">
-        <v>36.6820305513145</v>
+        <v>37.08871640907276</v>
       </c>
       <c r="O11" t="n">
-        <v>6.056569206350614</v>
+        <v>6.090050608087979</v>
       </c>
       <c r="P11" t="n">
-        <v>356.9757097302931</v>
+        <v>357.1449272893144</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31009,28 +31289,28 @@
         <v>0.0635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7461717933563277</v>
+        <v>0.7316095759406626</v>
       </c>
       <c r="J12" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K12" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3849039817780817</v>
+        <v>0.3773801990477211</v>
       </c>
       <c r="M12" t="n">
-        <v>6.032884232124621</v>
+        <v>6.042302763166149</v>
       </c>
       <c r="N12" t="n">
-        <v>50.36667118233732</v>
+        <v>50.50419408542595</v>
       </c>
       <c r="O12" t="n">
-        <v>7.096948018855522</v>
+        <v>7.106630290470016</v>
       </c>
       <c r="P12" t="n">
-        <v>356.3814499032266</v>
+        <v>356.5341696106444</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31087,28 +31367,28 @@
         <v>0.0636</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7518832998895356</v>
+        <v>0.7389760682695363</v>
       </c>
       <c r="J13" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K13" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4054232892598837</v>
+        <v>0.3993672892783199</v>
       </c>
       <c r="M13" t="n">
-        <v>5.881449261960145</v>
+        <v>5.883814499148104</v>
       </c>
       <c r="N13" t="n">
-        <v>46.93265896612409</v>
+        <v>46.97016670502033</v>
       </c>
       <c r="O13" t="n">
-        <v>6.850741490242067</v>
+        <v>6.85347843835671</v>
       </c>
       <c r="P13" t="n">
-        <v>358.2738655569951</v>
+        <v>358.4092238654677</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31165,28 +31445,28 @@
         <v>0.0607</v>
       </c>
       <c r="I14" t="n">
-        <v>0.769317124780533</v>
+        <v>0.7532570895072628</v>
       </c>
       <c r="J14" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K14" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3558083410806088</v>
+        <v>0.347882164712482</v>
       </c>
       <c r="M14" t="n">
-        <v>6.756778408713934</v>
+        <v>6.775159338446043</v>
       </c>
       <c r="N14" t="n">
-        <v>60.65754832937955</v>
+        <v>60.82823762267175</v>
       </c>
       <c r="O14" t="n">
-        <v>7.788295598484918</v>
+        <v>7.799245965006601</v>
       </c>
       <c r="P14" t="n">
-        <v>362.0467553826462</v>
+        <v>362.2151763898017</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31243,28 +31523,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5693678310285142</v>
+        <v>0.5517436347776622</v>
       </c>
       <c r="J15" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K15" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2634923963876332</v>
+        <v>0.2518734494135122</v>
       </c>
       <c r="M15" t="n">
-        <v>6.173763749468506</v>
+        <v>6.213072966923837</v>
       </c>
       <c r="N15" t="n">
-        <v>51.29441494220067</v>
+        <v>51.71210360870651</v>
       </c>
       <c r="O15" t="n">
-        <v>7.162011933961062</v>
+        <v>7.191112821302869</v>
       </c>
       <c r="P15" t="n">
-        <v>366.5547924252729</v>
+        <v>366.739627572147</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31321,28 +31601,28 @@
         <v>0.0795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2891351622391499</v>
+        <v>0.2779467532772262</v>
       </c>
       <c r="J16" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K16" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09391614869009546</v>
+        <v>0.08833660987677339</v>
       </c>
       <c r="M16" t="n">
-        <v>5.721602060354674</v>
+        <v>5.730082698586744</v>
       </c>
       <c r="N16" t="n">
-        <v>45.65675243239261</v>
+        <v>45.59758707412811</v>
       </c>
       <c r="O16" t="n">
-        <v>6.756978054751444</v>
+        <v>6.752598542348576</v>
       </c>
       <c r="P16" t="n">
-        <v>366.3593656573291</v>
+        <v>366.4767162673494</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31399,28 +31679,28 @@
         <v>0.0578</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1026659569532702</v>
+        <v>-0.09793532207463082</v>
       </c>
       <c r="J17" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K17" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L17" t="n">
-        <v>0.008001278160498781</v>
+        <v>0.007423437945386246</v>
       </c>
       <c r="M17" t="n">
-        <v>7.080918877271926</v>
+        <v>7.037083069652778</v>
       </c>
       <c r="N17" t="n">
-        <v>73.97410918378398</v>
+        <v>73.34364827042789</v>
       </c>
       <c r="O17" t="n">
-        <v>8.600820262264756</v>
+        <v>8.564090627172735</v>
       </c>
       <c r="P17" t="n">
-        <v>376.5741873424562</v>
+        <v>376.524579994678</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31458,7 +31738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R422"/>
+  <dimension ref="A1:R426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70285,6 +70565,374 @@
         </is>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-37.744281200292754,176.47048307077847</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-37.74494998393224,176.47079412175947</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-37.74558894500874,176.4711734242157</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-37.746193604574536,176.4715962607999</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-37.74678978701171,176.4720557199606</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-37.74737044027015,176.47256881000342</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-37.747925706484295,176.47312715557902</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>-37.74853802094842,176.47358621944295</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>-37.749162371431495,176.47402129134568</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>-37.74976001979281,176.47450798038548</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>-37.75033483323272,176.4750383133811</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>-37.75090364664277,176.47557844558986</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>-37.75147321996218,176.47611492228006</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>-37.75205459714125,176.47662165460108</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>-37.752631865832946,176.47714821666295</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>-37.753186112884336,176.47771589347767</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:59:31+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-37.74427926917684,176.47048831662724</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-37.7449496431454,176.47079504750462</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-37.74559145297566,176.47116701769323</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-37.7461945354064,176.47159431975177</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-37.746790709304584,176.47205404190774</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-37.747372307100036,176.4725654734373</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-37.74792324398984,176.47313148910536</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-37.74853722995341,176.4735875978818</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>-37.749162317339064,176.47402138198044</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>-37.74976321575851,176.47450277982486</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>-37.75033684064233,176.47503496552875</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>-37.75090444651094,176.47557707525547</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>-37.75147385897618,176.47611382519037</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>-37.752064147467756,176.4766063030464</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>-37.75264077677937,176.47713353217247</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>-37.753191620798276,176.4777059397992</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:59:03+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-37.74427684581538,176.4704948996527</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-37.74494884797603,176.47079720757657</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-37.7455909354587,176.4711683396741</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-37.74619332532499,176.47159684311436</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-37.74679086302006,176.47205376223226</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-37.74737095883402,176.47256788317952</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-37.747917847458915,176.4731409859812</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-37.74853643895839,176.47358897632057</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>-37.74916242552394,176.47402120071092</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>-37.749768615838015,176.47449399266972</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>-37.75034134375003,176.4750274554809</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>-37.750906579492664,176.47557342103022</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>-37.751475563013486,176.4761108996178</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>-37.75206842290405,176.4765994305468</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>-37.7526471183108,176.47712308185805</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>-37.75318961324097,176.47770956777563</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-37.744275520539425,176.47049849974456</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-37.74494710617638,176.47080193916258</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-37.74558970137974,176.47117149208992</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-37.74619039320437,176.47160295741566</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-37.74678681517901,176.47206112701951</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-37.74736717331763,176.47257464899374</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-37.74791643283419,176.47314347545327</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-37.74853353864314,176.47359403059588</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>-37.74916177641463,176.47402228832797</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>-37.74976751378102,176.47449578596678</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>-37.750339824629414,176.4750299889911</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>-37.750904873107295,176.47557634441043</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>-37.751474551241344,176.47611263667656</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>-37.75206386984201,176.4766067493126</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>-37.75264509558104,176.47712641514818</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>-37.753188120441855,176.4777122655016</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0220/nzd0220.xlsx
+++ b/data/nzd0220/nzd0220.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R426"/>
+  <dimension ref="A1:R427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26018,6 +26018,66 @@
         <v>376.64</v>
       </c>
       <c r="R426" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>384.34</v>
+      </c>
+      <c r="C427" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="D427" t="n">
+        <v>380.02</v>
+      </c>
+      <c r="E427" t="n">
+        <v>383.98</v>
+      </c>
+      <c r="F427" t="n">
+        <v>382.86</v>
+      </c>
+      <c r="G427" t="n">
+        <v>384.31</v>
+      </c>
+      <c r="H427" t="n">
+        <v>391.26</v>
+      </c>
+      <c r="I427" t="n">
+        <v>384.71</v>
+      </c>
+      <c r="J427" t="n">
+        <v>376.46</v>
+      </c>
+      <c r="K427" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="L427" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="M427" t="n">
+        <v>372.02</v>
+      </c>
+      <c r="N427" t="n">
+        <v>374.81</v>
+      </c>
+      <c r="O427" t="n">
+        <v>372.26</v>
+      </c>
+      <c r="P427" t="n">
+        <v>368.29</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>379.29</v>
+      </c>
+      <c r="R427" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26034,7 +26094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B430"/>
+  <dimension ref="A1:B431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30337,6 +30397,16 @@
       </c>
       <c r="B430" t="n">
         <v>0.51</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -30505,28 +30575,28 @@
         <v>0.0468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5510105464276933</v>
+        <v>0.5518893218041278</v>
       </c>
       <c r="J2" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K2" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4547114033270746</v>
+        <v>0.4566139401132655</v>
       </c>
       <c r="M2" t="n">
-        <v>3.604921753676527</v>
+        <v>3.601554483877778</v>
       </c>
       <c r="N2" t="n">
-        <v>20.8226143841386</v>
+        <v>20.78272037156258</v>
       </c>
       <c r="O2" t="n">
-        <v>4.56318029274963</v>
+        <v>4.558806902201779</v>
       </c>
       <c r="P2" t="n">
-        <v>367.6556255298736</v>
+        <v>367.6463590158723</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30587,28 +30657,28 @@
         <v>0.0542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8750069595426314</v>
+        <v>0.8724105479021985</v>
       </c>
       <c r="J3" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K3" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6226566925859829</v>
+        <v>0.6217196691131082</v>
       </c>
       <c r="M3" t="n">
-        <v>4.107139752556834</v>
+        <v>4.11183407270215</v>
       </c>
       <c r="N3" t="n">
-        <v>26.53602511468338</v>
+        <v>26.55217206545856</v>
       </c>
       <c r="O3" t="n">
-        <v>5.151312950567396</v>
+        <v>5.1528799777851</v>
       </c>
       <c r="P3" t="n">
-        <v>361.3271456069626</v>
+        <v>361.3545242585092</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30665,28 +30735,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9954694573757481</v>
+        <v>0.9927209394000361</v>
       </c>
       <c r="J4" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K4" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6967492229177437</v>
+        <v>0.6958654337877256</v>
       </c>
       <c r="M4" t="n">
-        <v>3.808070115008611</v>
+        <v>3.814495820471811</v>
       </c>
       <c r="N4" t="n">
-        <v>24.66642286671889</v>
+        <v>24.69641807747658</v>
       </c>
       <c r="O4" t="n">
-        <v>4.966530264351451</v>
+        <v>4.969549081906383</v>
       </c>
       <c r="P4" t="n">
-        <v>359.5580916480117</v>
+        <v>359.5870742310331</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30743,28 +30813,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9541082753007765</v>
+        <v>0.9519545314512978</v>
       </c>
       <c r="J5" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K5" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7060159441805923</v>
+        <v>0.7055806306528913</v>
       </c>
       <c r="M5" t="n">
-        <v>3.728645256315018</v>
+        <v>3.731771264886937</v>
       </c>
       <c r="N5" t="n">
-        <v>21.67851140109986</v>
+        <v>21.68159481467753</v>
       </c>
       <c r="O5" t="n">
-        <v>4.656018835990665</v>
+        <v>4.656349945469898</v>
       </c>
       <c r="P5" t="n">
-        <v>363.3013224744413</v>
+        <v>363.3240332809472</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30821,28 +30891,28 @@
         <v>0.0858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7930923670523912</v>
+        <v>0.7918370720593778</v>
       </c>
       <c r="J6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5654335436048329</v>
+        <v>0.565699681897078</v>
       </c>
       <c r="M6" t="n">
-        <v>4.292767614307616</v>
+        <v>4.289703301607117</v>
       </c>
       <c r="N6" t="n">
-        <v>27.64693781874201</v>
+        <v>27.60037350645535</v>
       </c>
       <c r="O6" t="n">
-        <v>5.258035547496993</v>
+        <v>5.253605762374576</v>
       </c>
       <c r="P6" t="n">
-        <v>364.4673489735792</v>
+        <v>364.4805858130953</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30899,28 +30969,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6987733071331342</v>
+        <v>0.6976040125112332</v>
       </c>
       <c r="J7" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K7" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L7" t="n">
-        <v>0.506013036753465</v>
+        <v>0.506258376583389</v>
       </c>
       <c r="M7" t="n">
-        <v>4.338048362848476</v>
+        <v>4.334871654676885</v>
       </c>
       <c r="N7" t="n">
-        <v>27.26159482746188</v>
+        <v>27.21350892155056</v>
       </c>
       <c r="O7" t="n">
-        <v>5.221263719394174</v>
+        <v>5.216656872130901</v>
       </c>
       <c r="P7" t="n">
-        <v>368.2535241675046</v>
+        <v>368.2658541499734</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30977,28 +31047,28 @@
         <v>0.058</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4767191065032322</v>
+        <v>0.4763041085324118</v>
       </c>
       <c r="J8" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K8" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L8" t="n">
-        <v>0.397650330428575</v>
+        <v>0.3983863646064584</v>
       </c>
       <c r="M8" t="n">
-        <v>3.625544123856279</v>
+        <v>3.619253574301966</v>
       </c>
       <c r="N8" t="n">
-        <v>19.68780545994116</v>
+        <v>19.64359383484907</v>
       </c>
       <c r="O8" t="n">
-        <v>4.437094258627054</v>
+        <v>4.432109411425792</v>
       </c>
       <c r="P8" t="n">
-        <v>379.4516830386358</v>
+        <v>379.4560591108497</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31055,28 +31125,28 @@
         <v>0.0577</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5913946498605185</v>
+        <v>0.5891711686200231</v>
       </c>
       <c r="J9" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K9" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4620661733383032</v>
+        <v>0.4608010297208799</v>
       </c>
       <c r="M9" t="n">
-        <v>3.994796786112533</v>
+        <v>3.995673542512429</v>
       </c>
       <c r="N9" t="n">
-        <v>23.28650571731058</v>
+        <v>23.28936626350741</v>
       </c>
       <c r="O9" t="n">
-        <v>4.82560936227857</v>
+        <v>4.825905745402349</v>
       </c>
       <c r="P9" t="n">
-        <v>373.8773723283205</v>
+        <v>373.9008185019379</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31133,28 +31203,28 @@
         <v>0.0703</v>
       </c>
       <c r="I10" t="n">
-        <v>0.791730940705796</v>
+        <v>0.7886344979270037</v>
       </c>
       <c r="J10" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K10" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5227266687100798</v>
+        <v>0.5211467199322106</v>
       </c>
       <c r="M10" t="n">
-        <v>4.771345169536504</v>
+        <v>4.775087276219663</v>
       </c>
       <c r="N10" t="n">
-        <v>32.73200499078949</v>
+        <v>32.76672866237666</v>
       </c>
       <c r="O10" t="n">
-        <v>5.721189123843879</v>
+        <v>5.724222974550927</v>
       </c>
       <c r="P10" t="n">
-        <v>362.2176988399434</v>
+        <v>362.2503502217791</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31211,28 +31281,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7460807408589123</v>
+        <v>0.742755880397191</v>
       </c>
       <c r="J11" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K11" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4618826872810469</v>
+        <v>0.4600223049627842</v>
       </c>
       <c r="M11" t="n">
-        <v>5.135086567865224</v>
+        <v>5.138731163604553</v>
       </c>
       <c r="N11" t="n">
-        <v>37.08871640907276</v>
+        <v>37.13027910068863</v>
       </c>
       <c r="O11" t="n">
-        <v>6.090050608087979</v>
+        <v>6.093461996327591</v>
       </c>
       <c r="P11" t="n">
-        <v>357.1449272893144</v>
+        <v>357.1799872908199</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31289,28 +31359,28 @@
         <v>0.0635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7316095759406626</v>
+        <v>0.7289727779108061</v>
       </c>
       <c r="J12" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K12" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3773801990477211</v>
+        <v>0.3764619911503668</v>
       </c>
       <c r="M12" t="n">
-        <v>6.042302763166149</v>
+        <v>6.040167499325666</v>
       </c>
       <c r="N12" t="n">
-        <v>50.50419408542595</v>
+        <v>50.46653686775079</v>
       </c>
       <c r="O12" t="n">
-        <v>7.106630290470016</v>
+        <v>7.103980353840429</v>
       </c>
       <c r="P12" t="n">
-        <v>356.5341696106444</v>
+        <v>356.561974128747</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31367,28 +31437,28 @@
         <v>0.0636</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7389760682695363</v>
+        <v>0.7362310125645577</v>
       </c>
       <c r="J13" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K13" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3993672892783199</v>
+        <v>0.3983131081281762</v>
       </c>
       <c r="M13" t="n">
-        <v>5.883814499148104</v>
+        <v>5.88228759985637</v>
       </c>
       <c r="N13" t="n">
-        <v>46.97016670502033</v>
+        <v>46.94758440220786</v>
       </c>
       <c r="O13" t="n">
-        <v>6.85347843835671</v>
+        <v>6.851830733622063</v>
       </c>
       <c r="P13" t="n">
-        <v>358.4092238654677</v>
+        <v>358.4381699395232</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31445,28 +31515,28 @@
         <v>0.0607</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7532570895072628</v>
+        <v>0.7498838901334876</v>
       </c>
       <c r="J14" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K14" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L14" t="n">
-        <v>0.347882164712482</v>
+        <v>0.3464679280961096</v>
       </c>
       <c r="M14" t="n">
-        <v>6.775159338446043</v>
+        <v>6.776243687765398</v>
       </c>
       <c r="N14" t="n">
-        <v>60.82823762267175</v>
+        <v>60.81784100051203</v>
       </c>
       <c r="O14" t="n">
-        <v>7.799245965006601</v>
+        <v>7.798579421953208</v>
       </c>
       <c r="P14" t="n">
-        <v>362.2151763898017</v>
+        <v>362.2507461156546</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31523,28 +31593,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5517436347776622</v>
+        <v>0.5476146711602682</v>
       </c>
       <c r="J15" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K15" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2518734494135122</v>
+        <v>0.2492548408785359</v>
       </c>
       <c r="M15" t="n">
-        <v>6.213072966923837</v>
+        <v>6.221140229239681</v>
       </c>
       <c r="N15" t="n">
-        <v>51.71210360870651</v>
+        <v>51.78907731375693</v>
       </c>
       <c r="O15" t="n">
-        <v>7.191112821302869</v>
+        <v>7.196462833486805</v>
       </c>
       <c r="P15" t="n">
-        <v>366.739627572147</v>
+        <v>366.7831666837303</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31601,28 +31671,28 @@
         <v>0.0795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2779467532772262</v>
+        <v>0.2754352516806488</v>
       </c>
       <c r="J16" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K16" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08833660987677339</v>
+        <v>0.08714796070999775</v>
       </c>
       <c r="M16" t="n">
-        <v>5.730082698586744</v>
+        <v>5.730495933554367</v>
       </c>
       <c r="N16" t="n">
-        <v>45.59758707412811</v>
+        <v>45.56394216479439</v>
       </c>
       <c r="O16" t="n">
-        <v>6.752598542348576</v>
+        <v>6.750106826176486</v>
       </c>
       <c r="P16" t="n">
-        <v>366.4767162673494</v>
+        <v>366.5031995591358</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31679,28 +31749,28 @@
         <v>0.0578</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09793532207463082</v>
+        <v>-0.09552561599401382</v>
       </c>
       <c r="J17" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K17" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L17" t="n">
-        <v>0.007423437945386246</v>
+        <v>0.007093238888713604</v>
       </c>
       <c r="M17" t="n">
-        <v>7.037083069652778</v>
+        <v>7.032101703933969</v>
       </c>
       <c r="N17" t="n">
-        <v>73.34364827042789</v>
+        <v>73.23904294728898</v>
       </c>
       <c r="O17" t="n">
-        <v>8.564090627172735</v>
+        <v>8.557981242517945</v>
       </c>
       <c r="P17" t="n">
-        <v>376.524579994678</v>
+        <v>376.4991701166435</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31738,7 +31808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R426"/>
+  <dimension ref="A1:R427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70933,6 +71003,98 @@
         </is>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-37.74426582708929,176.470524831841</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-37.74493775346643,176.4708273457183</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-37.745580744352665,176.47119437252397</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-37.74618303963075,176.47161829169286</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-37.7467707262876,176.4720903997102</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-37.74735472778178,176.4725968927616</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-37.7479041727512,176.47316505087383</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>-37.748524837696216,176.47360919341935</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>-37.74914933515124,176.47404313431795</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>-37.74975687892975,176.47451309128078</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>-37.75032669508483,176.47505188575363</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>-37.750899647301694,176.47558529726146</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>-37.75146736233335,176.47612497893456</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>-37.75206031623235,176.4766124615194</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>-37.75263842603907,176.47713740599545</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>-37.75317447934395,176.47773691713</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
